--- a/school_1/walls/vor_spartac_1_walls.xlsx
+++ b/school_1/walls/vor_spartac_1_walls.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="387">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -1197,7 +1197,16 @@
     <t>3.012</t>
   </si>
   <si>
-    <t>2.006</t>
+    <t>1.007</t>
+  </si>
+  <si>
+    <t>1.085</t>
+  </si>
+  <si>
+    <t>2.070</t>
+  </si>
+  <si>
+    <t>Лестницы</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +1954,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2467,12 +2476,66 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2506,51 +2569,36 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2572,38 +2620,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2911,7 +2932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="142"/>
@@ -2931,144 +2952,146 @@
       <c r="A1" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="219" t="s">
+      <c r="B1" s="187" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219" t="s">
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219" t="s">
+      <c r="G1" s="187"/>
+      <c r="H1" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219" t="s">
+      <c r="I1" s="187"/>
+      <c r="J1" s="187" t="s">
         <v>127</v>
       </c>
-      <c r="K1" s="219"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="171">
         <v>1</v>
       </c>
-      <c r="B2" s="222" t="s">
+      <c r="B2" s="192" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="219" t="s">
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="187" t="s">
         <v>372</v>
       </c>
-      <c r="G2" s="219"/>
-      <c r="H2" s="219" t="s">
+      <c r="G2" s="187"/>
+      <c r="H2" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="219"/>
-      <c r="J2" s="220">
-        <f>B15+E12</f>
-        <v>707.00800000000004</v>
-      </c>
-      <c r="K2" s="220"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="189">
+        <f>B17+E12+K16</f>
+        <v>1107.3760000000002</v>
+      </c>
+      <c r="K2" s="189"/>
     </row>
     <row r="3" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="171">
         <v>2</v>
       </c>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="192" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="187" t="s">
         <v>373</v>
       </c>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219" t="s">
+      <c r="G3" s="187"/>
+      <c r="H3" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="I3" s="219"/>
-      <c r="J3" s="221">
-        <f>B26+E22+H20+K21</f>
-        <v>1124.0320000000002</v>
-      </c>
-      <c r="K3" s="221"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="190">
+        <f>B29+E24+H22+H27+K28</f>
+        <v>1256.672</v>
+      </c>
+      <c r="K3" s="190"/>
     </row>
     <row r="4" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="171">
         <v>3</v>
       </c>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="192" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="222"/>
-      <c r="D4" s="222"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="219" t="s">
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="187" t="s">
         <v>374</v>
       </c>
-      <c r="G4" s="219"/>
-      <c r="H4" s="219" t="s">
+      <c r="G4" s="187"/>
+      <c r="H4" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="219"/>
-      <c r="J4" s="220">
-        <f>B37+E33+H31</f>
-        <v>881.952</v>
-      </c>
-      <c r="K4" s="220"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="189">
+        <f>B40+E36+H34+K40</f>
+        <v>1072.864</v>
+      </c>
+      <c r="K4" s="189"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="216"/>
-      <c r="B5" s="224"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="204" t="s">
+      <c r="A5" s="195"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="188" t="s">
         <v>298</v>
       </c>
-      <c r="I5" s="204"/>
-      <c r="J5" s="223">
+      <c r="I5" s="188"/>
+      <c r="J5" s="191">
         <f>SUM(J2:K4)</f>
-        <v>2712.9920000000002</v>
-      </c>
-      <c r="K5" s="223"/>
+        <v>3436.9120000000003</v>
+      </c>
+      <c r="K5" s="191"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="225"/>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="195"/>
-      <c r="J6" s="195"/>
-      <c r="K6" s="226"/>
+      <c r="A6" s="197"/>
+      <c r="B6" s="185"/>
+      <c r="C6" s="185"/>
+      <c r="D6" s="185"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="198"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="188" t="s">
         <v>361</v>
       </c>
-      <c r="B7" s="204"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="204" t="s">
+      <c r="B7" s="188"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="188" t="s">
         <v>363</v>
       </c>
-      <c r="E7" s="204"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="188" t="s">
+        <v>386</v>
+      </c>
+      <c r="K7" s="188"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="178" t="s">
@@ -3077,29 +3100,33 @@
       <c r="B8" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="182"/>
+      <c r="C8" s="183"/>
       <c r="D8" s="178" t="s">
         <v>304</v>
       </c>
       <c r="E8" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="182"/>
-      <c r="G8" s="182"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="182"/>
-      <c r="K8" s="182"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="181" t="s">
+        <v>304</v>
+      </c>
+      <c r="K8" s="181" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="178" t="s">
         <v>365</v>
       </c>
       <c r="B9" s="178">
-        <f>68.9*1.6</f>
-        <v>110.24000000000001</v>
-      </c>
-      <c r="C9" s="182"/>
+        <f>(68.9+22.69)*1.6</f>
+        <v>146.54400000000001</v>
+      </c>
+      <c r="C9" s="183"/>
       <c r="D9" s="178" t="s">
         <v>366</v>
       </c>
@@ -3107,12 +3134,17 @@
         <f>10.6*1.6</f>
         <v>16.96</v>
       </c>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
-      <c r="J9" s="182"/>
-      <c r="K9" s="182"/>
+      <c r="F9" s="183"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="183"/>
+      <c r="J9" s="181">
+        <v>1</v>
+      </c>
+      <c r="K9" s="229">
+        <f>22.6*1.6</f>
+        <v>36.160000000000004</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="178" t="s">
@@ -3122,7 +3154,7 @@
         <f>65.6*1.6</f>
         <v>104.96</v>
       </c>
-      <c r="C10" s="182"/>
+      <c r="C10" s="183"/>
       <c r="D10" s="178" t="s">
         <v>375</v>
       </c>
@@ -3130,12 +3162,17 @@
         <f>10.7*1.6</f>
         <v>17.12</v>
       </c>
-      <c r="F10" s="182"/>
-      <c r="G10" s="182"/>
-      <c r="H10" s="182"/>
-      <c r="I10" s="182"/>
-      <c r="J10" s="182"/>
-      <c r="K10" s="182"/>
+      <c r="F10" s="183"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="183"/>
+      <c r="J10" s="181">
+        <v>2</v>
+      </c>
+      <c r="K10" s="229">
+        <f>24.79*1.6</f>
+        <v>39.664000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="178" t="s">
@@ -3145,7 +3182,7 @@
         <f>68.2*1.6</f>
         <v>109.12</v>
       </c>
-      <c r="C11" s="182"/>
+      <c r="C11" s="183"/>
       <c r="D11" s="178" t="s">
         <v>376</v>
       </c>
@@ -3153,12 +3190,17 @@
         <f>10.7*1.6</f>
         <v>17.12</v>
       </c>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="182"/>
-      <c r="K11" s="182"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="183"/>
+      <c r="J11" s="181">
+        <v>3</v>
+      </c>
+      <c r="K11" s="229">
+        <f>(5.6+12.5)*1.6</f>
+        <v>28.960000000000004</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="178" t="s">
@@ -3168,7 +3210,7 @@
         <f>(24.58+53.3)*1.6</f>
         <v>124.608</v>
       </c>
-      <c r="C12" s="182"/>
+      <c r="C12" s="183"/>
       <c r="D12" s="178" t="s">
         <v>298</v>
       </c>
@@ -3176,12 +3218,17 @@
         <f>SUM(E9:E11)</f>
         <v>51.2</v>
       </c>
-      <c r="F12" s="182"/>
-      <c r="G12" s="182"/>
-      <c r="H12" s="182"/>
-      <c r="I12" s="182"/>
-      <c r="J12" s="182"/>
-      <c r="K12" s="182"/>
+      <c r="F12" s="183"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="183"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="181">
+        <v>4</v>
+      </c>
+      <c r="K12" s="229">
+        <f>(5.9+13.4)*1.6</f>
+        <v>30.880000000000003</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="178" t="s">
@@ -3191,548 +3238,721 @@
         <f>86.2*1.6</f>
         <v>137.92000000000002</v>
       </c>
-      <c r="C13" s="182"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
-      <c r="F13" s="182"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="182"/>
-      <c r="I13" s="182"/>
-      <c r="J13" s="182"/>
-      <c r="K13" s="182"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="185"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="181">
+        <v>5</v>
+      </c>
+      <c r="K13" s="229">
+        <f>(7.6+11.5+5.6)*1.6</f>
+        <v>39.52000000000001</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="178" t="s">
+      <c r="A14" s="181" t="s">
+        <v>383</v>
+      </c>
+      <c r="B14" s="181">
+        <f>25.08*1.6</f>
+        <v>40.128</v>
+      </c>
+      <c r="C14" s="183"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="181">
+        <v>6</v>
+      </c>
+      <c r="K14" s="229">
+        <f>(7.6+11.5+5.6)*1.6</f>
+        <v>39.52000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="181" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15" s="181">
+        <f>49.42*1.6</f>
+        <v>79.072000000000003</v>
+      </c>
+      <c r="C15" s="183"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="181">
+        <v>7</v>
+      </c>
+      <c r="K15" s="229">
+        <f>(6.8+1.2+10.85)*1.6</f>
+        <v>30.160000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="178" t="s">
         <v>371</v>
       </c>
-      <c r="B14" s="178">
+      <c r="B16" s="178">
         <f>43.1*1.6</f>
         <v>68.960000000000008</v>
       </c>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="182"/>
-      <c r="G14" s="182"/>
-      <c r="H14" s="182"/>
-      <c r="I14" s="182"/>
-      <c r="J14" s="182"/>
-      <c r="K14" s="182"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="179" t="s">
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="182" t="s">
         <v>298</v>
       </c>
-      <c r="B15" s="165">
-        <f>SUM(B9:B14)</f>
-        <v>655.80799999999999</v>
-      </c>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="182"/>
-      <c r="G15" s="182"/>
-      <c r="H15" s="182"/>
-      <c r="I15" s="182"/>
-      <c r="J15" s="182"/>
-      <c r="K15" s="182"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="198"/>
-      <c r="B16" s="198"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-      <c r="F16" s="182"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="200"/>
-      <c r="I16" s="182"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
+      <c r="K16" s="229">
+        <f>SUM(K9:K15)</f>
+        <v>244.86400000000003</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="218" t="s">
+      <c r="A17" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="165">
+        <f>SUM(B9:B16)</f>
+        <v>811.31200000000013</v>
+      </c>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="183"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="209"/>
+      <c r="K17" s="209"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="186"/>
+      <c r="B18" s="186"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="184"/>
+      <c r="E18" s="184"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="184"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="230"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="193" t="s">
         <v>361</v>
       </c>
-      <c r="B17" s="199"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="204" t="s">
+      <c r="B19" s="194"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="188" t="s">
         <v>363</v>
       </c>
-      <c r="E17" s="204"/>
-      <c r="F17" s="182"/>
-      <c r="G17" s="218" t="s">
+      <c r="E19" s="188"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="193" t="s">
         <v>362</v>
       </c>
-      <c r="H17" s="199"/>
-      <c r="I17" s="182"/>
-      <c r="J17" s="216" t="s">
-        <v>364</v>
-      </c>
-      <c r="K17" s="217"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="178" t="s">
+      <c r="H19" s="194"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="188" t="s">
+        <v>386</v>
+      </c>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="B18" s="178" t="s">
+      <c r="B20" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="182"/>
-      <c r="D18" s="178" t="s">
+      <c r="C20" s="183"/>
+      <c r="D20" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="178" t="s">
+      <c r="E20" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="182"/>
-      <c r="G18" s="178" t="s">
+      <c r="F20" s="183"/>
+      <c r="G20" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="H18" s="178" t="s">
+      <c r="H20" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="182"/>
-      <c r="J18" s="178" t="s">
+      <c r="I20" s="183"/>
+      <c r="J20" s="181" t="s">
         <v>304</v>
       </c>
-      <c r="K18" s="178" t="s">
+      <c r="K20" s="181" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="178" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="178" t="s">
         <v>340</v>
       </c>
-      <c r="B19" s="178">
+      <c r="B21" s="178">
         <f>66.1*1.6</f>
         <v>105.75999999999999</v>
       </c>
-      <c r="C19" s="182"/>
-      <c r="D19" s="178" t="s">
+      <c r="C21" s="183"/>
+      <c r="D21" s="178" t="s">
         <v>380</v>
       </c>
-      <c r="E19" s="178">
+      <c r="E21" s="178">
         <f>10.51*1.6</f>
         <v>16.815999999999999</v>
       </c>
-      <c r="F19" s="182"/>
-      <c r="G19" s="178" t="s">
+      <c r="F21" s="183"/>
+      <c r="G21" s="178" t="s">
         <v>285</v>
       </c>
-      <c r="H19" s="178">
+      <c r="H21" s="178">
         <f>136.3*1.6</f>
         <v>218.08000000000004</v>
       </c>
-      <c r="I19" s="182"/>
-      <c r="J19" s="178" t="s">
-        <v>341</v>
-      </c>
-      <c r="K19" s="178">
-        <f>72.2*1.6</f>
-        <v>115.52000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="178" t="s">
+      <c r="I21" s="183"/>
+      <c r="J21" s="181">
+        <v>1</v>
+      </c>
+      <c r="K21" s="229">
+        <f>(25.5)*1.6</f>
+        <v>40.800000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="178" t="s">
         <v>335</v>
       </c>
-      <c r="B20" s="178">
+      <c r="B22" s="178">
         <f>53.8*1.6</f>
         <v>86.08</v>
       </c>
-      <c r="C20" s="182"/>
-      <c r="D20" s="178" t="s">
+      <c r="C22" s="183"/>
+      <c r="D22" s="178" t="s">
         <v>336</v>
       </c>
-      <c r="E20" s="178">
+      <c r="E22" s="178">
         <f>8.6*1.6</f>
         <v>13.76</v>
       </c>
-      <c r="F20" s="182"/>
-      <c r="G20" s="178" t="s">
+      <c r="F22" s="183"/>
+      <c r="G22" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="165">
-        <f>SUM(H19:H19)</f>
+      <c r="H22" s="165">
+        <f>SUM(H21:H21)</f>
         <v>218.08000000000004</v>
       </c>
-      <c r="I20" s="182"/>
-      <c r="J20" s="178" t="s">
-        <v>383</v>
-      </c>
-      <c r="K20" s="178">
-        <f>33.1*1.6</f>
-        <v>52.960000000000008</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="178" t="s">
+      <c r="I22" s="183"/>
+      <c r="J22" s="181">
+        <v>2</v>
+      </c>
+      <c r="K22" s="229">
+        <f>(25.4+2.7)*1.6</f>
+        <v>44.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="178" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="178">
+      <c r="B23" s="178">
         <f>74.2*1.6</f>
         <v>118.72000000000001</v>
       </c>
-      <c r="C21" s="182"/>
-      <c r="D21" s="178" t="s">
+      <c r="C23" s="183"/>
+      <c r="D23" s="178" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="178">
+      <c r="E23" s="178">
         <f>8.67*1.6</f>
         <v>13.872</v>
       </c>
-      <c r="F21" s="182"/>
-      <c r="G21" s="195"/>
-      <c r="H21" s="195"/>
-      <c r="I21" s="182"/>
-      <c r="J21" s="178" t="s">
+      <c r="F23" s="183"/>
+      <c r="G23" s="199"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="181">
+        <v>3</v>
+      </c>
+      <c r="K23" s="229">
+        <f>(19.6)*1.6</f>
+        <v>31.360000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="178" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" s="178">
+        <f>(1.7 +1.2 + 43.6)*1.6</f>
+        <v>74.400000000000006</v>
+      </c>
+      <c r="C24" s="183"/>
+      <c r="D24" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="K21" s="165">
-        <f>SUM(K19:K20)</f>
-        <v>168.48000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="178" t="s">
-        <v>291</v>
-      </c>
-      <c r="B22" s="178">
-        <f>43.6*1.6</f>
-        <v>69.760000000000005</v>
-      </c>
-      <c r="C22" s="182"/>
-      <c r="D22" s="178" t="s">
-        <v>298</v>
-      </c>
-      <c r="E22" s="165">
-        <f>SUM(E19:E21)</f>
+      <c r="E24" s="165">
+        <f>SUM(E21:E23)</f>
         <v>44.448</v>
       </c>
-      <c r="F22" s="182"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="182"/>
-      <c r="I22" s="182"/>
-      <c r="J22" s="195"/>
-      <c r="K22" s="195"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="178" t="s">
+      <c r="F24" s="183"/>
+      <c r="G24" s="195" t="s">
+        <v>364</v>
+      </c>
+      <c r="H24" s="196"/>
+      <c r="I24" s="183"/>
+      <c r="J24" s="181">
+        <v>4</v>
+      </c>
+      <c r="K24" s="229">
+        <f>(20.8)*1.6</f>
+        <v>33.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="178" t="s">
         <v>345</v>
       </c>
-      <c r="B23" s="178">
+      <c r="B25" s="178">
         <f>61.04*1.6</f>
         <v>97.664000000000001</v>
       </c>
-      <c r="C23" s="182"/>
-      <c r="D23" s="195"/>
-      <c r="E23" s="195"/>
-      <c r="F23" s="182"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="182"/>
-      <c r="I23" s="182"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="182"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="178" t="s">
+      <c r="C25" s="183"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="185"/>
+      <c r="F25" s="183"/>
+      <c r="G25" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="H25" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="183"/>
+      <c r="J25" s="181">
+        <v>5</v>
+      </c>
+      <c r="K25" s="229">
+        <f>(28.7)*1.6</f>
+        <v>45.92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="181" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="181">
+        <f>(2.9+9.4)*1.6</f>
+        <v>19.680000000000003</v>
+      </c>
+      <c r="C26" s="183"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="208"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="178" t="s">
+        <v>341</v>
+      </c>
+      <c r="H26" s="178">
+        <f>6.8*1.6</f>
+        <v>10.88</v>
+      </c>
+      <c r="I26" s="183"/>
+      <c r="J26" s="181">
+        <v>6</v>
+      </c>
+      <c r="K26" s="229">
+        <f>(27.8)*1.6</f>
+        <v>44.480000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="178" t="s">
         <v>378</v>
       </c>
-      <c r="B24" s="178">
+      <c r="B27" s="178">
         <f>87.6*1.6</f>
         <v>140.16</v>
       </c>
-      <c r="C24" s="182"/>
-      <c r="D24" s="182"/>
-      <c r="E24" s="182"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="182"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="182"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="178" t="s">
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="H27" s="165">
+        <f>SUM(H26:H26)</f>
+        <v>10.88</v>
+      </c>
+      <c r="I27" s="183"/>
+      <c r="J27" s="181">
+        <v>7</v>
+      </c>
+      <c r="K27" s="229">
+        <f>(18.6)*1.6</f>
+        <v>29.760000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="178" t="s">
         <v>379</v>
       </c>
-      <c r="B25" s="178">
-        <f>46.8*1.6</f>
-        <v>74.88</v>
-      </c>
-      <c r="C25" s="182"/>
-      <c r="D25" s="182"/>
-      <c r="E25" s="182"/>
-      <c r="F25" s="182"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="182"/>
-      <c r="I25" s="182"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="182"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="179" t="s">
+      <c r="B28" s="178">
+        <f>43.9*1.6</f>
+        <v>70.239999999999995</v>
+      </c>
+      <c r="C28" s="183"/>
+      <c r="D28" s="183"/>
+      <c r="E28" s="183"/>
+      <c r="F28" s="183"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="182" t="s">
         <v>298</v>
       </c>
-      <c r="B26" s="165">
-        <f>SUM(B19:B25)</f>
-        <v>693.024</v>
-      </c>
-      <c r="C26" s="182"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="182"/>
-      <c r="F26" s="182"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="182"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="182"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="198"/>
-      <c r="B27" s="198"/>
-      <c r="C27" s="182"/>
-      <c r="D27" s="200"/>
-      <c r="E27" s="200"/>
-      <c r="F27" s="182"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="200"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="182"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="218" t="s">
+      <c r="K28" s="229">
+        <f>SUM(K21:K27)</f>
+        <v>270.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="B29" s="165">
+        <f>SUM(B21:B28)</f>
+        <v>712.70400000000006</v>
+      </c>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="209"/>
+      <c r="K29" s="209"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="186"/>
+      <c r="B30" s="186"/>
+      <c r="C30" s="183"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="184"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="184"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="183"/>
+      <c r="J30" s="230"/>
+      <c r="K30" s="230"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="193" t="s">
         <v>361</v>
       </c>
-      <c r="B28" s="199"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="204" t="s">
+      <c r="B31" s="194"/>
+      <c r="C31" s="183"/>
+      <c r="D31" s="188" t="s">
         <v>363</v>
       </c>
-      <c r="E28" s="204"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="218" t="s">
+      <c r="E31" s="188"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="193" t="s">
         <v>362</v>
       </c>
-      <c r="H28" s="199"/>
-      <c r="I28" s="182"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="182"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="178" t="s">
+      <c r="H31" s="194"/>
+      <c r="I31" s="183"/>
+      <c r="J31" s="188" t="s">
+        <v>386</v>
+      </c>
+      <c r="K31" s="188"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="B29" s="178" t="s">
+      <c r="B32" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="182"/>
-      <c r="D29" s="178" t="s">
+      <c r="C32" s="183"/>
+      <c r="D32" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="E29" s="178" t="s">
+      <c r="E32" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="182"/>
-      <c r="G29" s="178" t="s">
+      <c r="F32" s="183"/>
+      <c r="G32" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="H29" s="178" t="s">
+      <c r="H32" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="182"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="182"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="178" t="s">
+      <c r="I32" s="183"/>
+      <c r="J32" s="181" t="s">
+        <v>304</v>
+      </c>
+      <c r="K32" s="181" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="178" t="s">
         <v>283</v>
       </c>
-      <c r="B30" s="178">
-        <f>60.9*1.6</f>
-        <v>97.44</v>
-      </c>
-      <c r="C30" s="182"/>
-      <c r="D30" s="178" t="s">
+      <c r="B33" s="178">
+        <f>61.3*1.6</f>
+        <v>98.08</v>
+      </c>
+      <c r="C33" s="183"/>
+      <c r="D33" s="178" t="s">
         <v>377</v>
       </c>
-      <c r="E30" s="178">
+      <c r="E33" s="178">
         <f>10.05*1.6</f>
         <v>16.080000000000002</v>
       </c>
-      <c r="F30" s="182"/>
-      <c r="G30" s="178" t="s">
+      <c r="F33" s="183"/>
+      <c r="G33" s="178" t="s">
         <v>274</v>
       </c>
-      <c r="H30" s="178">
-        <f>106.4*1.6</f>
-        <v>170.24</v>
-      </c>
-      <c r="I30" s="182"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="182"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="178" t="s">
+      <c r="H33" s="178">
+        <f>104.3*1.6</f>
+        <v>166.88</v>
+      </c>
+      <c r="I33" s="183"/>
+      <c r="J33" s="181">
+        <v>1</v>
+      </c>
+      <c r="K33" s="229">
+        <f>(18.1)*1.6</f>
+        <v>28.960000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="178" t="s">
         <v>329</v>
       </c>
-      <c r="B31" s="178">
+      <c r="B34" s="178">
         <f>74.4*1.6</f>
         <v>119.04000000000002</v>
       </c>
-      <c r="C31" s="182"/>
-      <c r="D31" s="178" t="s">
+      <c r="C34" s="183"/>
+      <c r="D34" s="178" t="s">
         <v>353</v>
       </c>
-      <c r="E31" s="178">
+      <c r="E34" s="178">
         <f>8.25*1.6</f>
         <v>13.200000000000001</v>
       </c>
-      <c r="F31" s="182"/>
-      <c r="G31" s="178" t="s">
+      <c r="F34" s="183"/>
+      <c r="G34" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="H31" s="165">
-        <f>SUM(H30:H30)</f>
-        <v>170.24</v>
-      </c>
-      <c r="I31" s="182"/>
-      <c r="J31" s="182"/>
-      <c r="K31" s="182"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="178" t="s">
+      <c r="H34" s="165">
+        <f>SUM(H33:H33)</f>
+        <v>166.88</v>
+      </c>
+      <c r="I34" s="183"/>
+      <c r="J34" s="181">
+        <v>2</v>
+      </c>
+      <c r="K34" s="229">
+        <f>(2.7+16.5+1.8)*1.6</f>
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="178" t="s">
         <v>280</v>
       </c>
-      <c r="B32" s="178">
+      <c r="B35" s="178">
         <f>53.2*1.6</f>
         <v>85.12</v>
       </c>
-      <c r="C32" s="182"/>
-      <c r="D32" s="178" t="s">
+      <c r="C35" s="183"/>
+      <c r="D35" s="178" t="s">
         <v>346</v>
       </c>
-      <c r="E32" s="178">
+      <c r="E35" s="178">
         <f>8.17*1.6</f>
         <v>13.072000000000001</v>
       </c>
-      <c r="F32" s="182"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="195"/>
-      <c r="I32" s="182"/>
-      <c r="J32" s="182"/>
-      <c r="K32" s="182"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="178" t="s">
+      <c r="F35" s="183"/>
+      <c r="G35" s="185"/>
+      <c r="H35" s="185"/>
+      <c r="I35" s="183"/>
+      <c r="J35" s="181">
+        <v>3</v>
+      </c>
+      <c r="K35" s="229">
+        <f>(10.7+2.2)*1.6</f>
+        <v>20.64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="178" t="s">
         <v>284</v>
       </c>
-      <c r="B33" s="178">
+      <c r="B36" s="178">
         <f>46.56*1.6</f>
         <v>74.496000000000009</v>
       </c>
-      <c r="C33" s="182"/>
-      <c r="D33" s="178" t="s">
+      <c r="C36" s="183"/>
+      <c r="D36" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="E33" s="165">
-        <f>SUM(E30:E32)</f>
+      <c r="E36" s="165">
+        <f>SUM(E33:E35)</f>
         <v>42.352000000000004</v>
       </c>
-      <c r="F33" s="182"/>
-      <c r="G33" s="182"/>
-      <c r="H33" s="182"/>
-      <c r="I33" s="182"/>
-      <c r="J33" s="182"/>
-      <c r="K33" s="182"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="178" t="s">
+      <c r="F36" s="183"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="183"/>
+      <c r="I36" s="183"/>
+      <c r="J36" s="181">
+        <v>4</v>
+      </c>
+      <c r="K36" s="229">
+        <f>(14.6)*1.6</f>
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="178" t="s">
         <v>277</v>
       </c>
-      <c r="B34" s="178">
+      <c r="B37" s="178">
         <f>76.09*1.6</f>
         <v>121.74400000000001</v>
       </c>
-      <c r="C34" s="182"/>
-      <c r="D34" s="195"/>
-      <c r="E34" s="195"/>
-      <c r="F34" s="182"/>
-      <c r="G34" s="182"/>
-      <c r="H34" s="182"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="182"/>
-      <c r="K34" s="182"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="178" t="s">
+      <c r="C37" s="183"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="185"/>
+      <c r="F37" s="183"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="183"/>
+      <c r="I37" s="183"/>
+      <c r="J37" s="181">
+        <v>5</v>
+      </c>
+      <c r="K37" s="229">
+        <f>(21)*1.6</f>
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="178" t="s">
         <v>382</v>
       </c>
-      <c r="B35" s="178">
+      <c r="B38" s="178">
         <f>75.1*1.6</f>
         <v>120.16</v>
       </c>
-      <c r="C35" s="182"/>
-      <c r="D35" s="182"/>
-      <c r="E35" s="182"/>
-      <c r="F35" s="182"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="182"/>
-      <c r="I35" s="182"/>
-      <c r="J35" s="182"/>
-      <c r="K35" s="182"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="178" t="s">
+      <c r="C38" s="183"/>
+      <c r="D38" s="183"/>
+      <c r="E38" s="183"/>
+      <c r="F38" s="183"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="183"/>
+      <c r="I38" s="183"/>
+      <c r="J38" s="181">
+        <v>6</v>
+      </c>
+      <c r="K38" s="229">
+        <f>(20.7)*1.6</f>
+        <v>33.119999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="178" t="s">
         <v>381</v>
       </c>
-      <c r="B36" s="178">
-        <f>32.1*1.6</f>
-        <v>51.360000000000007</v>
-      </c>
-      <c r="C36" s="182"/>
-      <c r="D36" s="182"/>
-      <c r="E36" s="182"/>
-      <c r="F36" s="182"/>
-      <c r="G36" s="182"/>
-      <c r="H36" s="182"/>
-      <c r="I36" s="182"/>
-      <c r="J36" s="182"/>
-      <c r="K36" s="182"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="179" t="s">
+      <c r="B39" s="178">
+        <f>29.7*1.6</f>
+        <v>47.52</v>
+      </c>
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="183"/>
+      <c r="I39" s="183"/>
+      <c r="J39" s="181">
+        <v>7</v>
+      </c>
+      <c r="K39" s="229">
+        <f>(15.12)*1.6</f>
+        <v>24.192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="179" t="s">
         <v>298</v>
       </c>
-      <c r="B37" s="165">
-        <f>SUM(B30:B36)</f>
-        <v>669.36</v>
-      </c>
-      <c r="C37" s="182"/>
-      <c r="D37" s="182"/>
-      <c r="E37" s="182"/>
-      <c r="F37" s="182"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="182"/>
-      <c r="J37" s="182"/>
-      <c r="K37" s="182"/>
+      <c r="B40" s="165">
+        <f>SUM(B33:B39)</f>
+        <v>666.16</v>
+      </c>
+      <c r="C40" s="183"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
+      <c r="F40" s="183"/>
+      <c r="G40" s="183"/>
+      <c r="H40" s="183"/>
+      <c r="I40" s="183"/>
+      <c r="J40" s="182" t="s">
+        <v>298</v>
+      </c>
+      <c r="K40" s="229">
+        <f>SUM(K33:K39)</f>
+        <v>197.47200000000001</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="J7:K16"/>
-    <mergeCell ref="J22:K37"/>
-    <mergeCell ref="I7:I37"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D34:E37"/>
-    <mergeCell ref="D23:E27"/>
-    <mergeCell ref="D13:E16"/>
-    <mergeCell ref="G7:H16"/>
-    <mergeCell ref="G21:H27"/>
-    <mergeCell ref="G32:H37"/>
+  <mergeCells count="46">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G28:H30"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J17:K18"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="C7:C40"/>
+    <mergeCell ref="F7:F40"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="H4:I4"/>
@@ -3742,28 +3962,20 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="I7:I40"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D37:E40"/>
+    <mergeCell ref="D25:E30"/>
+    <mergeCell ref="D13:E18"/>
+    <mergeCell ref="G7:H18"/>
+    <mergeCell ref="G35:H40"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="C7:C37"/>
-    <mergeCell ref="F7:F37"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4188,15 +4400,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="212" t="s">
+      <c r="A2" s="225" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="213"/>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="213"/>
+      <c r="B2" s="226"/>
+      <c r="C2" s="226"/>
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
@@ -4205,13 +4417,13 @@
       <c r="B3" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="222" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="223"/>
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
@@ -4319,13 +4531,13 @@
       <c r="B9" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="209" t="s">
+      <c r="C9" s="222" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="210"/>
-      <c r="E9" s="210"/>
-      <c r="F9" s="210"/>
-      <c r="G9" s="211"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="224"/>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="117" t="s">
@@ -5802,13 +6014,13 @@
       <c r="B83" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C83" s="209" t="s">
+      <c r="C83" s="222" t="s">
         <v>230</v>
       </c>
-      <c r="D83" s="210"/>
-      <c r="E83" s="210"/>
-      <c r="F83" s="210"/>
-      <c r="G83" s="211"/>
+      <c r="D83" s="223"/>
+      <c r="E83" s="223"/>
+      <c r="F83" s="223"/>
+      <c r="G83" s="224"/>
     </row>
     <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
@@ -7188,11 +7400,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="214"/>
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
+      <c r="A4" s="227"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
@@ -7274,11 +7486,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="215"/>
-      <c r="B10" s="215"/>
-      <c r="C10" s="215"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="215"/>
+      <c r="A10" s="228"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="58"/>
@@ -7361,11 +7573,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="214"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="214"/>
+      <c r="A16" s="227"/>
+      <c r="B16" s="227"/>
+      <c r="C16" s="227"/>
+      <c r="D16" s="227"/>
+      <c r="E16" s="227"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
@@ -7571,11 +7783,11 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="214"/>
-      <c r="B7" s="214"/>
-      <c r="C7" s="214"/>
-      <c r="D7" s="214"/>
-      <c r="E7" s="214"/>
+      <c r="A7" s="227"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="227"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="227"/>
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -7663,11 +7875,11 @@
       <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="215"/>
-      <c r="B13" s="215"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="215"/>
-      <c r="E13" s="215"/>
+      <c r="A13" s="228"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
       <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -7756,11 +7968,11 @@
       <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="214"/>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="214"/>
+      <c r="A19" s="227"/>
+      <c r="B19" s="227"/>
+      <c r="C19" s="227"/>
+      <c r="D19" s="227"/>
+      <c r="E19" s="227"/>
       <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -8459,11 +8671,11 @@
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="201" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="185"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="203"/>
       <c r="E1" s="150" t="s">
         <v>270</v>
       </c>
@@ -8478,11 +8690,11 @@
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="204" t="s">
         <v>324</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="206"/>
       <c r="E2" s="152" t="s">
         <v>325</v>
       </c>
@@ -8495,13 +8707,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="189"/>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="189"/>
-      <c r="G3" s="189"/>
+      <c r="A3" s="207"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="174" t="s">
@@ -8510,11 +8722,11 @@
       <c r="B4" s="174" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="181"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
+      <c r="C4" s="200"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="174" t="s">
@@ -8523,11 +8735,11 @@
       <c r="B5" s="174">
         <v>190.5</v>
       </c>
-      <c r="C5" s="181"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="183"/>
+      <c r="E5" s="183"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="174" t="s">
@@ -8536,11 +8748,11 @@
       <c r="B6" s="174">
         <v>152.19999999999999</v>
       </c>
-      <c r="C6" s="181"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
+      <c r="C6" s="200"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="174" t="s">
@@ -8550,11 +8762,11 @@
         <f>SUM(B5:B6)</f>
         <v>342.7</v>
       </c>
-      <c r="C7" s="181"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9685,11 +9897,11 @@
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="201" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="185"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="203"/>
       <c r="E1" s="150" t="s">
         <v>270</v>
       </c>
@@ -9704,11 +9916,11 @@
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="204" t="s">
         <v>322</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="206"/>
       <c r="E2" s="152" t="s">
         <v>320</v>
       </c>
@@ -9723,11 +9935,11 @@
       <c r="A3" s="130">
         <v>2</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="204" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="188"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="206"/>
       <c r="E3" s="152" t="s">
         <v>321</v>
       </c>
@@ -9742,11 +9954,11 @@
       <c r="A4" s="130">
         <v>3</v>
       </c>
-      <c r="B4" s="186" t="s">
+      <c r="B4" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C4" s="187"/>
-      <c r="D4" s="188"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="206"/>
       <c r="E4" s="152" t="s">
         <v>319</v>
       </c>
@@ -9758,13 +9970,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="189"/>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
+      <c r="A5" s="207"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="175" t="s">
@@ -9773,15 +9985,15 @@
       <c r="B6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="193"/>
+      <c r="C6" s="211"/>
       <c r="D6" s="175" t="s">
         <v>304</v>
       </c>
       <c r="E6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="181"/>
-      <c r="G6" s="190"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="208"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="175" t="s">
@@ -9790,15 +10002,15 @@
       <c r="B7" s="175">
         <v>63.9</v>
       </c>
-      <c r="C7" s="193"/>
+      <c r="C7" s="211"/>
       <c r="D7" s="175" t="s">
         <v>329</v>
       </c>
       <c r="E7" s="175">
         <v>157.30000000000001</v>
       </c>
-      <c r="F7" s="181"/>
-      <c r="G7" s="190"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="208"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="175" t="s">
@@ -9807,15 +10019,15 @@
       <c r="B8" s="175">
         <v>143.4</v>
       </c>
-      <c r="C8" s="193"/>
+      <c r="C8" s="211"/>
       <c r="D8" s="175" t="s">
         <v>330</v>
       </c>
       <c r="E8" s="175">
         <v>18.600000000000001</v>
       </c>
-      <c r="F8" s="181"/>
-      <c r="G8" s="190"/>
+      <c r="F8" s="200"/>
+      <c r="G8" s="208"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="175" t="s">
@@ -9824,15 +10036,15 @@
       <c r="B9" s="175">
         <v>34.799999999999997</v>
       </c>
-      <c r="C9" s="193"/>
+      <c r="C9" s="211"/>
       <c r="D9" s="175" t="s">
         <v>331</v>
       </c>
       <c r="E9" s="175">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F9" s="181"/>
-      <c r="G9" s="190"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="208"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="175" t="s">
@@ -9842,59 +10054,59 @@
         <f>SUM(B7:B9)</f>
         <v>242.10000000000002</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="211"/>
       <c r="D10" s="175" t="s">
         <v>332</v>
       </c>
       <c r="E10" s="175">
         <v>20.6</v>
       </c>
-      <c r="F10" s="181"/>
-      <c r="G10" s="190"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="208"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="191"/>
-      <c r="B11" s="191"/>
-      <c r="C11" s="193"/>
+      <c r="A11" s="209"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="211"/>
       <c r="D11" s="175" t="s">
         <v>284</v>
       </c>
       <c r="E11" s="175">
         <v>104.1</v>
       </c>
-      <c r="F11" s="181"/>
-      <c r="G11" s="190"/>
+      <c r="F11" s="200"/>
+      <c r="G11" s="208"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="192"/>
-      <c r="B12" s="192"/>
-      <c r="C12" s="193"/>
+      <c r="A12" s="210"/>
+      <c r="B12" s="210"/>
+      <c r="C12" s="211"/>
       <c r="D12" s="175" t="s">
         <v>277</v>
       </c>
       <c r="E12" s="175">
         <v>108.2</v>
       </c>
-      <c r="F12" s="181"/>
-      <c r="G12" s="190"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="208"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="192"/>
-      <c r="B13" s="192"/>
-      <c r="C13" s="193"/>
+      <c r="A13" s="210"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="211"/>
       <c r="D13" s="175" t="s">
         <v>274</v>
       </c>
       <c r="E13" s="175">
         <v>305.39999999999998</v>
       </c>
-      <c r="F13" s="181"/>
-      <c r="G13" s="190"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="208"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="193"/>
+      <c r="A14" s="210"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="211"/>
       <c r="D14" s="175" t="s">
         <v>298</v>
       </c>
@@ -9902,8 +10114,8 @@
         <f>SUM(E7:E13)</f>
         <v>723.39999999999986</v>
       </c>
-      <c r="F14" s="181"/>
-      <c r="G14" s="190"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9940,11 +10152,11 @@
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="201" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="185"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="203"/>
       <c r="E1" s="150" t="s">
         <v>270</v>
       </c>
@@ -9959,11 +10171,11 @@
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="204" t="s">
         <v>318</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="206"/>
       <c r="E2" s="152" t="s">
         <v>309</v>
       </c>
@@ -9979,11 +10191,11 @@
       <c r="A3" s="130">
         <v>2</v>
       </c>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="204" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="188"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="206"/>
       <c r="E3" s="152" t="s">
         <v>310</v>
       </c>
@@ -9999,11 +10211,11 @@
       <c r="A4" s="130">
         <v>3</v>
       </c>
-      <c r="B4" s="186" t="s">
+      <c r="B4" s="204" t="s">
         <v>312</v>
       </c>
-      <c r="C4" s="187"/>
-      <c r="D4" s="188"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="206"/>
       <c r="E4" s="152" t="s">
         <v>315</v>
       </c>
@@ -10015,13 +10227,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="189"/>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
+      <c r="A5" s="207"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="175" t="s">
@@ -10030,15 +10242,15 @@
       <c r="B6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="193"/>
+      <c r="C6" s="211"/>
       <c r="D6" s="175" t="s">
         <v>304</v>
       </c>
       <c r="E6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="181"/>
-      <c r="G6" s="190"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="208"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="175" t="s">
@@ -10047,15 +10259,15 @@
       <c r="B7" s="175">
         <v>63.9</v>
       </c>
-      <c r="C7" s="193"/>
+      <c r="C7" s="211"/>
       <c r="D7" s="175" t="s">
         <v>329</v>
       </c>
       <c r="E7" s="175">
         <v>157.30000000000001</v>
       </c>
-      <c r="F7" s="181"/>
-      <c r="G7" s="190"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="208"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="175" t="s">
@@ -10064,15 +10276,15 @@
       <c r="B8" s="175">
         <v>143.4</v>
       </c>
-      <c r="C8" s="193"/>
+      <c r="C8" s="211"/>
       <c r="D8" s="175" t="s">
         <v>330</v>
       </c>
       <c r="E8" s="175">
         <v>18.600000000000001</v>
       </c>
-      <c r="F8" s="181"/>
-      <c r="G8" s="190"/>
+      <c r="F8" s="200"/>
+      <c r="G8" s="208"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="175" t="s">
@@ -10081,15 +10293,15 @@
       <c r="B9" s="175">
         <v>34.799999999999997</v>
       </c>
-      <c r="C9" s="193"/>
+      <c r="C9" s="211"/>
       <c r="D9" s="175" t="s">
         <v>331</v>
       </c>
       <c r="E9" s="175">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F9" s="181"/>
-      <c r="G9" s="190"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="208"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="175" t="s">
@@ -10099,59 +10311,59 @@
         <f>SUM(B7:B9)</f>
         <v>242.10000000000002</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="211"/>
       <c r="D10" s="175" t="s">
         <v>332</v>
       </c>
       <c r="E10" s="175">
         <v>20.6</v>
       </c>
-      <c r="F10" s="181"/>
-      <c r="G10" s="190"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="208"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="191"/>
-      <c r="B11" s="191"/>
-      <c r="C11" s="193"/>
+      <c r="A11" s="209"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="211"/>
       <c r="D11" s="175" t="s">
         <v>284</v>
       </c>
       <c r="E11" s="175">
         <v>104.1</v>
       </c>
-      <c r="F11" s="181"/>
-      <c r="G11" s="190"/>
+      <c r="F11" s="200"/>
+      <c r="G11" s="208"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="192"/>
-      <c r="B12" s="192"/>
-      <c r="C12" s="193"/>
+      <c r="A12" s="210"/>
+      <c r="B12" s="210"/>
+      <c r="C12" s="211"/>
       <c r="D12" s="175" t="s">
         <v>277</v>
       </c>
       <c r="E12" s="175">
         <v>108.2</v>
       </c>
-      <c r="F12" s="181"/>
-      <c r="G12" s="190"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="208"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="192"/>
-      <c r="B13" s="192"/>
-      <c r="C13" s="193"/>
+      <c r="A13" s="210"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="211"/>
       <c r="D13" s="175" t="s">
         <v>274</v>
       </c>
       <c r="E13" s="175">
         <v>305.39999999999998</v>
       </c>
-      <c r="F13" s="181"/>
-      <c r="G13" s="190"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="208"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="193"/>
+      <c r="A14" s="210"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="211"/>
       <c r="D14" s="175" t="s">
         <v>298</v>
       </c>
@@ -10159,8 +10371,8 @@
         <f>SUM(E7:E13)</f>
         <v>723.39999999999986</v>
       </c>
-      <c r="F14" s="181"/>
-      <c r="G14" s="190"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -10197,15 +10409,15 @@
       <c r="A1" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="212" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="208"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="201" t="s">
+      <c r="C1" s="214"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="212" t="s">
         <v>270</v>
       </c>
-      <c r="F1" s="202"/>
+      <c r="F1" s="213"/>
       <c r="G1" s="170" t="s">
         <v>49</v>
       </c>
@@ -10217,15 +10429,15 @@
       <c r="A2" s="171">
         <v>1</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="206"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="201" t="s">
+      <c r="C2" s="216"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="212" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="202"/>
+      <c r="F2" s="213"/>
       <c r="G2" s="170" t="s">
         <v>70</v>
       </c>
@@ -10238,15 +10450,15 @@
       <c r="A3" s="171">
         <v>2</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="201" t="s">
+      <c r="C3" s="216"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="212" t="s">
         <v>301</v>
       </c>
-      <c r="F3" s="202"/>
+      <c r="F3" s="213"/>
       <c r="G3" s="170" t="s">
         <v>70</v>
       </c>
@@ -10259,15 +10471,15 @@
       <c r="A4" s="171">
         <v>3</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="201" t="s">
+      <c r="C4" s="216"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="212" t="s">
         <v>316</v>
       </c>
-      <c r="F4" s="202"/>
+      <c r="F4" s="213"/>
       <c r="G4" s="170" t="s">
         <v>70</v>
       </c>
@@ -10279,15 +10491,15 @@
       <c r="A5" s="171">
         <v>4</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
-      <c r="E5" s="201" t="s">
+      <c r="C5" s="216"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="212" t="s">
         <v>317</v>
       </c>
-      <c r="F5" s="202"/>
+      <c r="F5" s="213"/>
       <c r="G5" s="170" t="s">
         <v>70</v>
       </c>
@@ -10299,15 +10511,15 @@
       <c r="A6" s="171">
         <v>5</v>
       </c>
-      <c r="B6" s="205" t="s">
+      <c r="B6" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="207"/>
-      <c r="E6" s="201" t="s">
+      <c r="C6" s="216"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="212" t="s">
         <v>302</v>
       </c>
-      <c r="F6" s="202"/>
+      <c r="F6" s="213"/>
       <c r="G6" s="170" t="s">
         <v>70</v>
       </c>
@@ -10320,15 +10532,15 @@
       <c r="A7" s="171">
         <v>6</v>
       </c>
-      <c r="B7" s="205" t="s">
+      <c r="B7" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="206"/>
-      <c r="D7" s="207"/>
-      <c r="E7" s="201" t="s">
+      <c r="C7" s="216"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="212" t="s">
         <v>300</v>
       </c>
-      <c r="F7" s="202"/>
+      <c r="F7" s="213"/>
       <c r="G7" s="170" t="s">
         <v>70</v>
       </c>
@@ -10341,15 +10553,15 @@
       <c r="A8" s="171">
         <v>7</v>
       </c>
-      <c r="B8" s="205" t="s">
+      <c r="B8" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="206"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="201" t="s">
+      <c r="C8" s="216"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="212" t="s">
         <v>303</v>
       </c>
-      <c r="F8" s="202"/>
+      <c r="F8" s="213"/>
       <c r="G8" s="170" t="s">
         <v>70</v>
       </c>
@@ -10359,12 +10571,12 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="191"/>
-      <c r="B9" s="191"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="203"/>
+      <c r="A9" s="209"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="218"/>
       <c r="G9" s="167" t="s">
         <v>298</v>
       </c>
@@ -10374,18 +10586,18 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="204" t="s">
+      <c r="A10" s="188" t="s">
         <v>305</v>
       </c>
-      <c r="B10" s="204"/>
-      <c r="C10" s="197"/>
-      <c r="D10" s="204" t="s">
+      <c r="B10" s="188"/>
+      <c r="C10" s="221"/>
+      <c r="D10" s="188" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="204"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="199"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="210"/>
+      <c r="G10" s="186"/>
+      <c r="H10" s="194"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="164" t="s">
@@ -10394,18 +10606,18 @@
       <c r="B11" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="197"/>
+      <c r="C11" s="221"/>
       <c r="D11" s="164" t="s">
         <v>304</v>
       </c>
       <c r="E11" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="192"/>
-      <c r="G11" s="196" t="s">
+      <c r="F11" s="210"/>
+      <c r="G11" s="219" t="s">
         <v>297</v>
       </c>
-      <c r="H11" s="196"/>
+      <c r="H11" s="219"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="164" t="s">
@@ -10414,14 +10626,14 @@
       <c r="B12" s="164">
         <v>523.6</v>
       </c>
-      <c r="C12" s="197"/>
+      <c r="C12" s="221"/>
       <c r="D12" s="175" t="s">
         <v>330</v>
       </c>
       <c r="E12" s="175">
         <v>73.099999999999994</v>
       </c>
-      <c r="F12" s="192"/>
+      <c r="F12" s="210"/>
       <c r="G12" s="164" t="s">
         <v>304</v>
       </c>
@@ -10436,14 +10648,14 @@
       <c r="B13" s="164">
         <v>88.4</v>
       </c>
-      <c r="C13" s="197"/>
+      <c r="C13" s="221"/>
       <c r="D13" s="175" t="s">
         <v>274</v>
       </c>
       <c r="E13" s="175">
         <v>301.2</v>
       </c>
-      <c r="F13" s="192"/>
+      <c r="F13" s="210"/>
       <c r="G13" s="164" t="s">
         <v>283</v>
       </c>
@@ -10458,14 +10670,14 @@
       <c r="B14" s="164">
         <v>84.1</v>
       </c>
-      <c r="C14" s="197"/>
+      <c r="C14" s="221"/>
       <c r="D14" s="175" t="s">
         <v>275</v>
       </c>
       <c r="E14" s="175">
         <v>79.3</v>
       </c>
-      <c r="F14" s="192"/>
+      <c r="F14" s="210"/>
       <c r="G14" s="164" t="s">
         <v>298</v>
       </c>
@@ -10481,16 +10693,16 @@
       <c r="B15" s="164">
         <v>32.1</v>
       </c>
-      <c r="C15" s="197"/>
+      <c r="C15" s="221"/>
       <c r="D15" s="175" t="s">
         <v>276</v>
       </c>
       <c r="E15" s="175">
         <v>137.1</v>
       </c>
-      <c r="F15" s="192"/>
-      <c r="G15" s="195"/>
-      <c r="H15" s="195"/>
+      <c r="F15" s="210"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="185"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="164" t="s">
@@ -10499,16 +10711,16 @@
       <c r="B16" s="164">
         <v>34.6</v>
       </c>
-      <c r="C16" s="197"/>
+      <c r="C16" s="221"/>
       <c r="D16" s="175" t="s">
         <v>277</v>
       </c>
       <c r="E16" s="175">
         <v>356.9</v>
       </c>
-      <c r="F16" s="192"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="200"/>
+      <c r="F16" s="210"/>
+      <c r="G16" s="184"/>
+      <c r="H16" s="184"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="164" t="s">
@@ -10517,18 +10729,18 @@
       <c r="B17" s="164">
         <v>112.9</v>
       </c>
-      <c r="C17" s="197"/>
+      <c r="C17" s="221"/>
       <c r="D17" s="175" t="s">
         <v>278</v>
       </c>
       <c r="E17" s="175">
         <v>115.1</v>
       </c>
-      <c r="F17" s="192"/>
-      <c r="G17" s="196" t="s">
+      <c r="F17" s="210"/>
+      <c r="G17" s="219" t="s">
         <v>296</v>
       </c>
-      <c r="H17" s="196"/>
+      <c r="H17" s="219"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="164" t="s">
@@ -10537,14 +10749,14 @@
       <c r="B18" s="164">
         <v>181.3</v>
       </c>
-      <c r="C18" s="197"/>
+      <c r="C18" s="221"/>
       <c r="D18" s="175" t="s">
         <v>279</v>
       </c>
       <c r="E18" s="175">
         <v>117.9</v>
       </c>
-      <c r="F18" s="192"/>
+      <c r="F18" s="210"/>
       <c r="G18" s="164" t="s">
         <v>304</v>
       </c>
@@ -10559,14 +10771,14 @@
       <c r="B19" s="164">
         <v>278.60000000000002</v>
       </c>
-      <c r="C19" s="197"/>
+      <c r="C19" s="221"/>
       <c r="D19" s="175" t="s">
         <v>280</v>
       </c>
       <c r="E19" s="175">
         <v>244.2</v>
       </c>
-      <c r="F19" s="192"/>
+      <c r="F19" s="210"/>
       <c r="G19" s="164" t="s">
         <v>336</v>
       </c>
@@ -10581,14 +10793,14 @@
       <c r="B20" s="164">
         <v>367</v>
       </c>
-      <c r="C20" s="197"/>
+      <c r="C20" s="221"/>
       <c r="D20" s="175" t="s">
         <v>281</v>
       </c>
       <c r="E20" s="175">
         <v>259.60000000000002</v>
       </c>
-      <c r="F20" s="192"/>
+      <c r="F20" s="210"/>
       <c r="G20" s="164" t="s">
         <v>333</v>
       </c>
@@ -10603,14 +10815,14 @@
       <c r="B21" s="164">
         <v>89.2</v>
       </c>
-      <c r="C21" s="197"/>
+      <c r="C21" s="221"/>
       <c r="D21" s="175" t="s">
         <v>347</v>
       </c>
       <c r="E21" s="175">
         <v>70.7</v>
       </c>
-      <c r="F21" s="192"/>
+      <c r="F21" s="210"/>
       <c r="G21" s="164" t="s">
         <v>298</v>
       </c>
@@ -10626,16 +10838,16 @@
       <c r="B22" s="164">
         <v>230.9</v>
       </c>
-      <c r="C22" s="197"/>
+      <c r="C22" s="221"/>
       <c r="D22" s="175" t="s">
         <v>348</v>
       </c>
       <c r="E22" s="175">
         <v>175.7</v>
       </c>
-      <c r="F22" s="192"/>
-      <c r="G22" s="195"/>
-      <c r="H22" s="195"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="185"/>
+      <c r="H22" s="185"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="164" t="s">
@@ -10644,16 +10856,16 @@
       <c r="B23" s="164">
         <v>269.60000000000002</v>
       </c>
-      <c r="C23" s="197"/>
+      <c r="C23" s="221"/>
       <c r="D23" s="175" t="s">
         <v>329</v>
       </c>
       <c r="E23" s="175">
         <v>352.3</v>
       </c>
-      <c r="F23" s="192"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="200"/>
+      <c r="F23" s="210"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="164" t="s">
@@ -10662,18 +10874,18 @@
       <c r="B24" s="164">
         <v>89.8</v>
       </c>
-      <c r="C24" s="197"/>
+      <c r="C24" s="221"/>
       <c r="D24" s="175" t="s">
         <v>349</v>
       </c>
       <c r="E24" s="175">
         <v>86.2</v>
       </c>
-      <c r="F24" s="192"/>
-      <c r="G24" s="196" t="s">
+      <c r="F24" s="210"/>
+      <c r="G24" s="219" t="s">
         <v>296</v>
       </c>
-      <c r="H24" s="196"/>
+      <c r="H24" s="219"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="164" t="s">
@@ -10682,14 +10894,14 @@
       <c r="B25" s="164">
         <v>65</v>
       </c>
-      <c r="C25" s="197"/>
+      <c r="C25" s="221"/>
       <c r="D25" s="175" t="s">
         <v>350</v>
       </c>
       <c r="E25" s="175">
         <v>86.7</v>
       </c>
-      <c r="F25" s="192"/>
+      <c r="F25" s="210"/>
       <c r="G25" s="164" t="s">
         <v>304</v>
       </c>
@@ -10704,14 +10916,14 @@
       <c r="B26" s="164">
         <v>93.7</v>
       </c>
-      <c r="C26" s="197"/>
+      <c r="C26" s="221"/>
       <c r="D26" s="175" t="s">
         <v>351</v>
       </c>
       <c r="E26" s="175">
         <v>31.6</v>
       </c>
-      <c r="F26" s="192"/>
+      <c r="F26" s="210"/>
       <c r="G26" s="164" t="s">
         <v>353</v>
       </c>
@@ -10726,14 +10938,14 @@
       <c r="B27" s="164">
         <v>221.1</v>
       </c>
-      <c r="C27" s="197"/>
+      <c r="C27" s="221"/>
       <c r="D27" s="175" t="s">
         <v>352</v>
       </c>
       <c r="E27" s="175">
         <v>34.299999999999997</v>
       </c>
-      <c r="F27" s="192"/>
+      <c r="F27" s="210"/>
       <c r="G27" s="164" t="s">
         <v>346</v>
       </c>
@@ -10748,14 +10960,14 @@
       <c r="B28" s="164">
         <v>280.3</v>
       </c>
-      <c r="C28" s="197"/>
+      <c r="C28" s="221"/>
       <c r="D28" s="175" t="s">
         <v>354</v>
       </c>
       <c r="E28" s="175">
         <v>109.4</v>
       </c>
-      <c r="F28" s="192"/>
+      <c r="F28" s="210"/>
       <c r="G28" s="164" t="s">
         <v>298</v>
       </c>
@@ -10771,16 +10983,16 @@
       <c r="B29" s="164">
         <v>116.4</v>
       </c>
-      <c r="C29" s="197"/>
+      <c r="C29" s="221"/>
       <c r="D29" s="175" t="s">
         <v>282</v>
       </c>
       <c r="E29" s="175">
         <v>172.5</v>
       </c>
-      <c r="F29" s="192"/>
-      <c r="G29" s="195"/>
-      <c r="H29" s="195"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="164" t="s">
@@ -10789,16 +11001,16 @@
       <c r="B30" s="164">
         <v>31.2</v>
       </c>
-      <c r="C30" s="197"/>
+      <c r="C30" s="221"/>
       <c r="D30" s="175" t="s">
         <v>355</v>
       </c>
       <c r="E30" s="175">
         <v>98.9</v>
       </c>
-      <c r="F30" s="192"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="182"/>
+      <c r="F30" s="210"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="183"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="164" t="s">
@@ -10807,16 +11019,16 @@
       <c r="B31" s="164">
         <v>165.5</v>
       </c>
-      <c r="C31" s="197"/>
+      <c r="C31" s="221"/>
       <c r="D31" s="175" t="s">
         <v>323</v>
       </c>
       <c r="E31" s="175">
         <v>223.7</v>
       </c>
-      <c r="F31" s="192"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="182"/>
+      <c r="F31" s="210"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="183"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="164" t="s">
@@ -10825,16 +11037,16 @@
       <c r="B32" s="164">
         <v>239.3</v>
       </c>
-      <c r="C32" s="197"/>
+      <c r="C32" s="221"/>
       <c r="D32" s="175" t="s">
         <v>356</v>
       </c>
       <c r="E32" s="175">
         <v>227.1</v>
       </c>
-      <c r="F32" s="192"/>
-      <c r="G32" s="182"/>
-      <c r="H32" s="182"/>
+      <c r="F32" s="210"/>
+      <c r="G32" s="183"/>
+      <c r="H32" s="183"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="164" t="s">
@@ -10843,16 +11055,16 @@
       <c r="B33" s="164">
         <v>200.9</v>
       </c>
-      <c r="C33" s="197"/>
+      <c r="C33" s="221"/>
       <c r="D33" s="175" t="s">
         <v>357</v>
       </c>
       <c r="E33" s="175">
         <v>165.6</v>
       </c>
-      <c r="F33" s="192"/>
-      <c r="G33" s="182"/>
-      <c r="H33" s="182"/>
+      <c r="F33" s="210"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="183"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="164" t="s">
@@ -10861,16 +11073,16 @@
       <c r="B34" s="180">
         <v>247.4</v>
       </c>
-      <c r="C34" s="197"/>
+      <c r="C34" s="221"/>
       <c r="D34" s="175" t="s">
         <v>358</v>
       </c>
       <c r="E34" s="175">
         <v>136.19999999999999</v>
       </c>
-      <c r="F34" s="192"/>
-      <c r="G34" s="182"/>
-      <c r="H34" s="182"/>
+      <c r="F34" s="210"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="183"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="179" t="s">
@@ -10880,63 +11092,63 @@
         <f>SUM(B12:B34)</f>
         <v>4042.9000000000005</v>
       </c>
-      <c r="C35" s="192"/>
+      <c r="C35" s="210"/>
       <c r="D35" s="175" t="s">
         <v>359</v>
       </c>
       <c r="E35" s="175">
         <v>52.9</v>
       </c>
-      <c r="F35" s="192"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="182"/>
+      <c r="F35" s="210"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="183"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="191"/>
-      <c r="B36" s="191"/>
-      <c r="C36" s="192"/>
+      <c r="A36" s="209"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="210"/>
       <c r="D36" s="175" t="s">
         <v>360</v>
       </c>
       <c r="E36" s="175">
         <v>43.8</v>
       </c>
-      <c r="F36" s="192"/>
-      <c r="G36" s="182"/>
-      <c r="H36" s="182"/>
+      <c r="F36" s="210"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="183"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="194"/>
-      <c r="B37" s="194"/>
-      <c r="C37" s="192"/>
+      <c r="A37" s="220"/>
+      <c r="B37" s="220"/>
+      <c r="C37" s="210"/>
       <c r="D37" s="175" t="s">
         <v>331</v>
       </c>
       <c r="E37" s="175">
         <v>49.2</v>
       </c>
-      <c r="F37" s="192"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="182"/>
+      <c r="F37" s="210"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="183"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="194"/>
-      <c r="B38" s="194"/>
-      <c r="C38" s="192"/>
+      <c r="A38" s="220"/>
+      <c r="B38" s="220"/>
+      <c r="C38" s="210"/>
       <c r="D38" s="175" t="s">
         <v>332</v>
       </c>
       <c r="E38" s="175">
         <v>46.2</v>
       </c>
-      <c r="F38" s="192"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="182"/>
+      <c r="F38" s="210"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="183"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="194"/>
-      <c r="B39" s="194"/>
-      <c r="C39" s="192"/>
+      <c r="A39" s="220"/>
+      <c r="B39" s="220"/>
+      <c r="C39" s="210"/>
       <c r="D39" s="175" t="s">
         <v>298</v>
       </c>
@@ -10944,12 +11156,27 @@
         <f>SUM(E12:E38)</f>
         <v>3847.3999999999996</v>
       </c>
-      <c r="F39" s="192"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="182"/>
+      <c r="F39" s="210"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A36:B39"/>
+    <mergeCell ref="G29:H39"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="F10:F39"/>
+    <mergeCell ref="C10:C39"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="G22:H23"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
@@ -10964,21 +11191,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A36:B39"/>
-    <mergeCell ref="G29:H39"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="F10:F39"/>
-    <mergeCell ref="C10:C39"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="G22:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
